--- a/StructureDefinition-resq-stroke-discharge-composition.xlsx
+++ b/StructureDefinition-resq-stroke-discharge-composition.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-resq-stroke-discharge-composition.xlsx
+++ b/StructureDefinition-resq-stroke-discharge-composition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12856" uniqueCount="879">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12876" uniqueCount="879">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1579,6 +1579,12 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Classification of a section of a composition/document.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/doc-section-codes|5.0.0</t>
+  </si>
+  <si>
     <t>Composition.section:alerts.author</t>
   </si>
   <si>
@@ -1606,6 +1612,12 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>If a section is empty, why it is empty.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|5.0.0</t>
+  </si>
+  <si>
     <t>Composition.section:alerts.section</t>
   </si>
   <si>
@@ -1935,12 +1947,6 @@
     <t>Composition.section.section.code</t>
   </si>
   <si>
-    <t>Classification of a section of a composition/document.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/doc-section-codes|5.0.0</t>
-  </si>
-  <si>
     <t>Composition.section:hospitalCourse.section.author</t>
   </si>
   <si>
@@ -1975,12 +1981,6 @@
   </si>
   <si>
     <t>Composition.section.section.emptyReason</t>
-  </si>
-  <si>
-    <t>If a section is empty, why it is empty.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|5.0.0</t>
   </si>
   <si>
     <t>Composition.section:hospitalCourse.section.section</t>
@@ -10736,7 +10736,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>492</v>
       </c>
@@ -10749,13 +10749,13 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>79</v>
@@ -10855,7 +10855,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>494</v>
       </c>
@@ -10868,13 +10868,13 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>79</v>
@@ -10920,11 +10920,13 @@
         <v>79</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>79</v>
@@ -10974,7 +10976,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>441</v>
@@ -11091,7 +11093,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>445</v>
@@ -11206,9 +11208,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>451</v>
@@ -11219,13 +11221,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>79</v>
@@ -11325,7 +11327,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>457</v>
@@ -11442,9 +11444,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>465</v>
@@ -11461,7 +11463,7 @@
         <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>79</v>
@@ -11561,7 +11563,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>472</v>
@@ -11609,7 +11611,7 @@
         <v>79</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>79</v>
@@ -11624,11 +11626,13 @@
         <v>79</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>477</v>
+        <v>506</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>79</v>
@@ -11678,7 +11682,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>480</v>
@@ -11795,13 +11799,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>418</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>79</v>
@@ -11826,7 +11830,7 @@
         <v>337</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>488</v>
@@ -11912,7 +11916,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>426</v>
@@ -12027,7 +12031,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>427</v>
@@ -12144,7 +12148,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>428</v>
@@ -12261,9 +12265,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>429</v>
@@ -12274,13 +12278,13 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>79</v>
@@ -12311,7 +12315,7 @@
         <v>79</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>79</v>
@@ -12380,9 +12384,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>435</v>
@@ -12393,13 +12397,13 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>79</v>
@@ -12430,7 +12434,7 @@
         <v>79</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>79</v>
@@ -12445,11 +12449,13 @@
         <v>79</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -12499,7 +12505,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>441</v>
@@ -12616,7 +12622,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>445</v>
@@ -12731,9 +12737,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>451</v>
@@ -12744,13 +12750,13 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>79</v>
@@ -12850,7 +12856,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>457</v>
@@ -12967,9 +12973,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>465</v>
@@ -12986,7 +12992,7 @@
         <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>79</v>
@@ -13086,7 +13092,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>472</v>
@@ -13134,7 +13140,7 @@
         <v>79</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>79</v>
@@ -13149,11 +13155,13 @@
         <v>79</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>477</v>
+        <v>506</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>79</v>
@@ -13203,7 +13211,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>480</v>
@@ -13320,13 +13328,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>418</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>79</v>
@@ -13351,7 +13359,7 @@
         <v>337</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="M87" t="s" s="2">
         <v>488</v>
@@ -13437,7 +13445,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>426</v>
@@ -13552,7 +13560,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>427</v>
@@ -13669,7 +13677,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>428</v>
@@ -13786,9 +13794,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>429</v>
@@ -13799,13 +13807,13 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>79</v>
@@ -13836,7 +13844,7 @@
         <v>79</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>79</v>
@@ -13905,9 +13913,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>435</v>
@@ -13918,13 +13926,13 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>79</v>
@@ -13955,7 +13963,7 @@
         <v>79</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>79</v>
@@ -13970,11 +13978,13 @@
         <v>79</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y92" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="Z92" t="s" s="2">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -14024,7 +14034,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>441</v>
@@ -14141,7 +14151,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>445</v>
@@ -14256,9 +14266,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>451</v>
@@ -14269,13 +14279,13 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>79</v>
@@ -14375,7 +14385,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>457</v>
@@ -14492,9 +14502,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>465</v>
@@ -14511,7 +14521,7 @@
         <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>79</v>
@@ -14611,7 +14621,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>472</v>
@@ -14674,11 +14684,13 @@
         <v>79</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>477</v>
+        <v>506</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>79</v>
@@ -14728,7 +14740,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>480</v>
@@ -14845,13 +14857,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>418</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>79</v>
@@ -14876,7 +14888,7 @@
         <v>337</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>488</v>
@@ -14962,7 +14974,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>426</v>
@@ -15077,7 +15089,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>427</v>
@@ -15194,7 +15206,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>428</v>
@@ -15311,9 +15323,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>429</v>
@@ -15324,13 +15336,13 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>79</v>
@@ -15361,7 +15373,7 @@
         <v>79</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>79</v>
@@ -15430,9 +15442,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>435</v>
@@ -15443,13 +15455,13 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>79</v>
@@ -15480,7 +15492,7 @@
         <v>79</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>79</v>
@@ -15495,11 +15507,13 @@
         <v>79</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y105" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="Z105" t="s" s="2">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>79</v>
@@ -15549,7 +15563,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>441</v>
@@ -15666,7 +15680,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>445</v>
@@ -15781,9 +15795,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>451</v>
@@ -15794,13 +15808,13 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>79</v>
@@ -15900,7 +15914,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>457</v>
@@ -16017,9 +16031,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>465</v>
@@ -16036,7 +16050,7 @@
         <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>79</v>
@@ -16045,7 +16059,7 @@
         <v>79</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="L110" t="s" s="2">
         <v>466</v>
@@ -16136,7 +16150,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>472</v>
@@ -16199,11 +16213,13 @@
         <v>79</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>477</v>
+        <v>506</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>79</v>
@@ -16253,7 +16269,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>480</v>
@@ -16370,13 +16386,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>418</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>79</v>
@@ -16401,7 +16417,7 @@
         <v>337</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>488</v>
@@ -16487,7 +16503,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>426</v>
@@ -16602,7 +16618,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>427</v>
@@ -16719,7 +16735,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>428</v>
@@ -16836,9 +16852,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>429</v>
@@ -16849,13 +16865,13 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>79</v>
@@ -16886,7 +16902,7 @@
         <v>79</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>79</v>
@@ -16955,9 +16971,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>435</v>
@@ -16968,13 +16984,13 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>79</v>
@@ -17005,7 +17021,7 @@
         <v>79</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>79</v>
@@ -17020,11 +17036,13 @@
         <v>79</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y118" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="Z118" t="s" s="2">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>79</v>
@@ -17074,7 +17092,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>441</v>
@@ -17191,7 +17209,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>445</v>
@@ -17306,9 +17324,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>451</v>
@@ -17319,13 +17337,13 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>79</v>
@@ -17425,7 +17443,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>457</v>
@@ -17542,9 +17560,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>465</v>
@@ -17561,7 +17579,7 @@
         <v>81</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>79</v>
@@ -17570,7 +17588,7 @@
         <v>79</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="L123" t="s" s="2">
         <v>466</v>
@@ -17661,7 +17679,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>472</v>
@@ -17724,11 +17742,13 @@
         <v>79</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y124" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="Z124" t="s" s="2">
-        <v>477</v>
+        <v>506</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>79</v>
@@ -17778,7 +17798,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>480</v>
@@ -17895,13 +17915,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>418</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>79</v>
@@ -17926,7 +17946,7 @@
         <v>337</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="M126" t="s" s="2">
         <v>488</v>
@@ -18012,7 +18032,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>426</v>
@@ -18127,7 +18147,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>427</v>
@@ -18244,7 +18264,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>428</v>
@@ -18361,9 +18381,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>429</v>
@@ -18374,13 +18394,13 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>79</v>
@@ -18411,7 +18431,7 @@
         <v>79</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>79</v>
@@ -18480,9 +18500,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>435</v>
@@ -18493,13 +18513,13 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>79</v>
@@ -18530,7 +18550,7 @@
         <v>79</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>79</v>
@@ -18545,11 +18565,13 @@
         <v>79</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y131" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="Z131" t="s" s="2">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>79</v>
@@ -18599,7 +18621,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>441</v>
@@ -18716,7 +18738,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>445</v>
@@ -18831,9 +18853,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>451</v>
@@ -18844,13 +18866,13 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>79</v>
@@ -18950,7 +18972,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>457</v>
@@ -19067,9 +19089,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>465</v>
@@ -19086,7 +19108,7 @@
         <v>81</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>79</v>
@@ -19186,7 +19208,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>472</v>
@@ -19249,11 +19271,13 @@
         <v>79</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y137" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="Z137" t="s" s="2">
-        <v>477</v>
+        <v>506</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>79</v>
@@ -19303,7 +19327,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>480</v>
@@ -19314,7 +19338,7 @@
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="G138" t="s" s="2">
         <v>81</v>
@@ -19418,10 +19442,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19533,10 +19557,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19650,10 +19674,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19769,10 +19793,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19888,10 +19912,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19954,10 +19978,10 @@
         <v>265</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>603</v>
+        <v>497</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>79</v>
@@ -20007,10 +20031,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20124,10 +20148,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20241,10 +20265,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20358,10 +20382,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20477,10 +20501,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20594,10 +20618,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20660,10 +20684,10 @@
         <v>356</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>617</v>
+        <v>506</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>79</v>
@@ -20952,7 +20976,7 @@
         <v>623</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21067,7 +21091,7 @@
         <v>624</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21184,7 +21208,7 @@
         <v>625</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21303,7 +21327,7 @@
         <v>626</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21422,7 +21446,7 @@
         <v>628</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21485,10 +21509,10 @@
         <v>265</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>603</v>
+        <v>497</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>79</v>
@@ -21541,7 +21565,7 @@
         <v>630</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21658,7 +21682,7 @@
         <v>631</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21775,7 +21799,7 @@
         <v>632</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21892,7 +21916,7 @@
         <v>633</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22011,7 +22035,7 @@
         <v>634</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22128,7 +22152,7 @@
         <v>636</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22191,10 +22215,10 @@
         <v>356</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>617</v>
+        <v>506</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>79</v>
@@ -22483,7 +22507,7 @@
         <v>641</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22598,7 +22622,7 @@
         <v>642</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22715,7 +22739,7 @@
         <v>643</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22834,7 +22858,7 @@
         <v>644</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22953,7 +22977,7 @@
         <v>646</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23016,10 +23040,10 @@
         <v>265</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>603</v>
+        <v>497</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>79</v>
@@ -23072,7 +23096,7 @@
         <v>648</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23189,7 +23213,7 @@
         <v>649</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23306,7 +23330,7 @@
         <v>650</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23423,7 +23447,7 @@
         <v>651</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23542,7 +23566,7 @@
         <v>652</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23659,7 +23683,7 @@
         <v>654</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23722,10 +23746,10 @@
         <v>356</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>617</v>
+        <v>506</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>79</v>
@@ -24014,7 +24038,7 @@
         <v>659</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24129,7 +24153,7 @@
         <v>660</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24246,7 +24270,7 @@
         <v>661</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24365,7 +24389,7 @@
         <v>662</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24484,7 +24508,7 @@
         <v>664</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24547,10 +24571,10 @@
         <v>265</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>603</v>
+        <v>497</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>79</v>
@@ -24603,7 +24627,7 @@
         <v>666</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24720,7 +24744,7 @@
         <v>667</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24837,7 +24861,7 @@
         <v>668</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24954,7 +24978,7 @@
         <v>669</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25073,7 +25097,7 @@
         <v>670</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25190,7 +25214,7 @@
         <v>672</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25253,10 +25277,10 @@
         <v>356</v>
       </c>
       <c r="Y188" t="s" s="2">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="Z188" t="s" s="2">
-        <v>617</v>
+        <v>506</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>79</v>
@@ -25545,7 +25569,7 @@
         <v>677</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25660,7 +25684,7 @@
         <v>678</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25777,7 +25801,7 @@
         <v>679</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25896,7 +25920,7 @@
         <v>680</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26015,7 +26039,7 @@
         <v>682</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26078,10 +26102,10 @@
         <v>265</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>603</v>
+        <v>497</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>79</v>
@@ -26134,7 +26158,7 @@
         <v>684</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26251,7 +26275,7 @@
         <v>685</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26368,7 +26392,7 @@
         <v>686</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26485,7 +26509,7 @@
         <v>687</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26604,7 +26628,7 @@
         <v>688</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26721,7 +26745,7 @@
         <v>689</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26766,7 +26790,7 @@
         <v>79</v>
       </c>
       <c r="S201" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="T201" t="s" s="2">
         <v>79</v>
@@ -26784,10 +26808,10 @@
         <v>356</v>
       </c>
       <c r="Y201" t="s" s="2">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>617</v>
+        <v>506</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>79</v>
@@ -27076,7 +27100,7 @@
         <v>694</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27191,7 +27215,7 @@
         <v>695</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27308,7 +27332,7 @@
         <v>696</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27427,7 +27451,7 @@
         <v>697</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27546,7 +27570,7 @@
         <v>699</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27609,10 +27633,10 @@
         <v>265</v>
       </c>
       <c r="Y208" t="s" s="2">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="Z208" t="s" s="2">
-        <v>603</v>
+        <v>497</v>
       </c>
       <c r="AA208" t="s" s="2">
         <v>79</v>
@@ -27665,7 +27689,7 @@
         <v>701</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27782,7 +27806,7 @@
         <v>702</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27899,7 +27923,7 @@
         <v>703</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28016,7 +28040,7 @@
         <v>704</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28135,7 +28159,7 @@
         <v>705</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28252,7 +28276,7 @@
         <v>707</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28315,10 +28339,10 @@
         <v>356</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>617</v>
+        <v>506</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>79</v>
@@ -28607,7 +28631,7 @@
         <v>712</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28722,7 +28746,7 @@
         <v>713</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28839,7 +28863,7 @@
         <v>714</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28958,7 +28982,7 @@
         <v>715</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29077,7 +29101,7 @@
         <v>717</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29140,10 +29164,10 @@
         <v>265</v>
       </c>
       <c r="Y221" t="s" s="2">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="Z221" t="s" s="2">
-        <v>603</v>
+        <v>497</v>
       </c>
       <c r="AA221" t="s" s="2">
         <v>79</v>
@@ -29196,7 +29220,7 @@
         <v>719</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29313,7 +29337,7 @@
         <v>720</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29430,7 +29454,7 @@
         <v>721</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29547,7 +29571,7 @@
         <v>722</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29666,7 +29690,7 @@
         <v>723</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29783,7 +29807,7 @@
         <v>725</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29846,10 +29870,10 @@
         <v>356</v>
       </c>
       <c r="Y227" t="s" s="2">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="Z227" t="s" s="2">
-        <v>617</v>
+        <v>506</v>
       </c>
       <c r="AA227" t="s" s="2">
         <v>79</v>
@@ -30482,7 +30506,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
         <v>733</v>
       </c>
@@ -30495,13 +30519,13 @@
       </c>
       <c r="E233" s="2"/>
       <c r="F233" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G233" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H233" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I233" t="s" s="2">
         <v>79</v>
@@ -30601,7 +30625,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
         <v>735</v>
       </c>
@@ -30614,13 +30638,13 @@
       </c>
       <c r="E234" s="2"/>
       <c r="F234" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G234" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H234" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I234" t="s" s="2">
         <v>79</v>
@@ -30666,11 +30690,13 @@
         <v>79</v>
       </c>
       <c r="X234" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y234" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="Y234" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="Z234" t="s" s="2">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>79</v>
@@ -30952,7 +30978,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
         <v>739</v>
       </c>
@@ -30965,13 +30991,13 @@
       </c>
       <c r="E237" s="2"/>
       <c r="F237" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G237" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H237" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I237" t="s" s="2">
         <v>79</v>
@@ -31188,7 +31214,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
         <v>741</v>
       </c>
@@ -31207,7 +31233,7 @@
         <v>81</v>
       </c>
       <c r="H239" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I239" t="s" s="2">
         <v>79</v>
@@ -31370,11 +31396,13 @@
         <v>79</v>
       </c>
       <c r="X240" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y240" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="Y240" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="Z240" t="s" s="2">
-        <v>477</v>
+        <v>506</v>
       </c>
       <c r="AA240" t="s" s="2">
         <v>79</v>
@@ -31435,7 +31463,7 @@
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="G241" t="s" s="2">
         <v>81</v>
@@ -31542,7 +31570,7 @@
         <v>744</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -31657,7 +31685,7 @@
         <v>745</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31774,7 +31802,7 @@
         <v>746</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31893,7 +31921,7 @@
         <v>747</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -32012,7 +32040,7 @@
         <v>748</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -32075,10 +32103,10 @@
         <v>265</v>
       </c>
       <c r="Y246" t="s" s="2">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="Z246" t="s" s="2">
-        <v>603</v>
+        <v>497</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>79</v>
@@ -32131,7 +32159,7 @@
         <v>749</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32248,7 +32276,7 @@
         <v>750</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32365,7 +32393,7 @@
         <v>751</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32482,7 +32510,7 @@
         <v>752</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32601,7 +32629,7 @@
         <v>753</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32718,7 +32746,7 @@
         <v>754</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32781,10 +32809,10 @@
         <v>356</v>
       </c>
       <c r="Y252" t="s" s="2">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="Z252" t="s" s="2">
-        <v>617</v>
+        <v>506</v>
       </c>
       <c r="AA252" t="s" s="2">
         <v>79</v>
@@ -33073,7 +33101,7 @@
         <v>759</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -33188,7 +33216,7 @@
         <v>760</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -33305,7 +33333,7 @@
         <v>761</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -33424,7 +33452,7 @@
         <v>762</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33543,7 +33571,7 @@
         <v>764</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33606,10 +33634,10 @@
         <v>265</v>
       </c>
       <c r="Y259" t="s" s="2">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="Z259" t="s" s="2">
-        <v>603</v>
+        <v>497</v>
       </c>
       <c r="AA259" t="s" s="2">
         <v>79</v>
@@ -33662,7 +33690,7 @@
         <v>766</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33779,7 +33807,7 @@
         <v>767</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33896,7 +33924,7 @@
         <v>768</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -34013,7 +34041,7 @@
         <v>769</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -34132,7 +34160,7 @@
         <v>770</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -34249,7 +34277,7 @@
         <v>772</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34312,10 +34340,10 @@
         <v>356</v>
       </c>
       <c r="Y265" t="s" s="2">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="Z265" t="s" s="2">
-        <v>617</v>
+        <v>506</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>79</v>
@@ -34604,7 +34632,7 @@
         <v>777</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34719,7 +34747,7 @@
         <v>778</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34836,7 +34864,7 @@
         <v>779</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34955,7 +34983,7 @@
         <v>780</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -35074,7 +35102,7 @@
         <v>782</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -35137,10 +35165,10 @@
         <v>265</v>
       </c>
       <c r="Y272" t="s" s="2">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="Z272" t="s" s="2">
-        <v>603</v>
+        <v>497</v>
       </c>
       <c r="AA272" t="s" s="2">
         <v>79</v>
@@ -35193,7 +35221,7 @@
         <v>784</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -35310,7 +35338,7 @@
         <v>785</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -35427,7 +35455,7 @@
         <v>786</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -35544,7 +35572,7 @@
         <v>787</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -35663,7 +35691,7 @@
         <v>788</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35780,7 +35808,7 @@
         <v>789</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35825,7 +35853,7 @@
         <v>79</v>
       </c>
       <c r="S278" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="T278" t="s" s="2">
         <v>79</v>
@@ -35843,10 +35871,10 @@
         <v>356</v>
       </c>
       <c r="Y278" t="s" s="2">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="Z278" t="s" s="2">
-        <v>617</v>
+        <v>506</v>
       </c>
       <c r="AA278" t="s" s="2">
         <v>79</v>
@@ -36135,7 +36163,7 @@
         <v>794</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -36250,7 +36278,7 @@
         <v>795</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -36367,7 +36395,7 @@
         <v>796</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36486,7 +36514,7 @@
         <v>797</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -36605,7 +36633,7 @@
         <v>799</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -36668,10 +36696,10 @@
         <v>265</v>
       </c>
       <c r="Y285" t="s" s="2">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="Z285" t="s" s="2">
-        <v>603</v>
+        <v>497</v>
       </c>
       <c r="AA285" t="s" s="2">
         <v>79</v>
@@ -36724,7 +36752,7 @@
         <v>801</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36841,7 +36869,7 @@
         <v>802</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36958,7 +36986,7 @@
         <v>803</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -37075,7 +37103,7 @@
         <v>804</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -37194,7 +37222,7 @@
         <v>805</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -37311,7 +37339,7 @@
         <v>806</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
@@ -37356,7 +37384,7 @@
         <v>79</v>
       </c>
       <c r="S291" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="T291" t="s" s="2">
         <v>79</v>
@@ -37374,10 +37402,10 @@
         <v>356</v>
       </c>
       <c r="Y291" t="s" s="2">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="Z291" t="s" s="2">
-        <v>617</v>
+        <v>506</v>
       </c>
       <c r="AA291" t="s" s="2">
         <v>79</v>
@@ -37666,7 +37694,7 @@
         <v>811</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -37781,7 +37809,7 @@
         <v>812</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37898,7 +37926,7 @@
         <v>813</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -38017,7 +38045,7 @@
         <v>814</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -38136,7 +38164,7 @@
         <v>816</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -38199,10 +38227,10 @@
         <v>265</v>
       </c>
       <c r="Y298" t="s" s="2">
-        <v>602</v>
+        <v>496</v>
       </c>
       <c r="Z298" t="s" s="2">
-        <v>603</v>
+        <v>497</v>
       </c>
       <c r="AA298" t="s" s="2">
         <v>79</v>
@@ -38255,7 +38283,7 @@
         <v>818</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -38372,7 +38400,7 @@
         <v>819</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -38489,7 +38517,7 @@
         <v>820</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" t="s" s="2">
@@ -38606,7 +38634,7 @@
         <v>821</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C302" s="2"/>
       <c r="D302" t="s" s="2">
@@ -38725,7 +38753,7 @@
         <v>822</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" t="s" s="2">
@@ -38842,7 +38870,7 @@
         <v>824</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
@@ -38905,10 +38933,10 @@
         <v>356</v>
       </c>
       <c r="Y304" t="s" s="2">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="Z304" t="s" s="2">
-        <v>617</v>
+        <v>506</v>
       </c>
       <c r="AA304" t="s" s="2">
         <v>79</v>
@@ -39541,7 +39569,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
         <v>832</v>
       </c>
@@ -39554,13 +39582,13 @@
       </c>
       <c r="E310" s="2"/>
       <c r="F310" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G310" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H310" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I310" t="s" s="2">
         <v>79</v>
@@ -39660,7 +39688,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" hidden="true">
       <c r="A311" t="s" s="2">
         <v>834</v>
       </c>
@@ -39673,13 +39701,13 @@
       </c>
       <c r="E311" s="2"/>
       <c r="F311" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G311" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H311" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I311" t="s" s="2">
         <v>79</v>
@@ -39725,11 +39753,13 @@
         <v>79</v>
       </c>
       <c r="X311" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y311" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="Y311" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="Z311" t="s" s="2">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="AA311" t="s" s="2">
         <v>79</v>
@@ -40011,7 +40041,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" hidden="true">
       <c r="A314" t="s" s="2">
         <v>838</v>
       </c>
@@ -40024,13 +40054,13 @@
       </c>
       <c r="E314" s="2"/>
       <c r="F314" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G314" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H314" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I314" t="s" s="2">
         <v>79</v>
@@ -40247,7 +40277,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
         <v>840</v>
       </c>
@@ -40266,7 +40296,7 @@
         <v>81</v>
       </c>
       <c r="H316" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I316" t="s" s="2">
         <v>79</v>
@@ -40429,11 +40459,13 @@
         <v>79</v>
       </c>
       <c r="X317" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y317" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="Y317" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="Z317" t="s" s="2">
-        <v>477</v>
+        <v>506</v>
       </c>
       <c r="AA317" t="s" s="2">
         <v>79</v>
@@ -41066,7 +41098,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" hidden="true">
       <c r="A323" t="s" s="2">
         <v>850</v>
       </c>
@@ -41079,13 +41111,13 @@
       </c>
       <c r="E323" s="2"/>
       <c r="F323" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G323" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H323" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I323" t="s" s="2">
         <v>79</v>
@@ -41185,7 +41217,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" hidden="true">
       <c r="A324" t="s" s="2">
         <v>852</v>
       </c>
@@ -41198,13 +41230,13 @@
       </c>
       <c r="E324" s="2"/>
       <c r="F324" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G324" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H324" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I324" t="s" s="2">
         <v>79</v>
@@ -41250,11 +41282,13 @@
         <v>79</v>
       </c>
       <c r="X324" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y324" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="Y324" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="Z324" t="s" s="2">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="AA324" t="s" s="2">
         <v>79</v>
@@ -41536,7 +41570,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" hidden="true">
       <c r="A327" t="s" s="2">
         <v>856</v>
       </c>
@@ -41549,13 +41583,13 @@
       </c>
       <c r="E327" s="2"/>
       <c r="F327" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G327" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H327" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I327" t="s" s="2">
         <v>79</v>
@@ -41772,7 +41806,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="329">
+    <row r="329" hidden="true">
       <c r="A329" t="s" s="2">
         <v>858</v>
       </c>
@@ -41791,7 +41825,7 @@
         <v>81</v>
       </c>
       <c r="H329" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I329" t="s" s="2">
         <v>79</v>
@@ -41954,11 +41988,13 @@
         <v>79</v>
       </c>
       <c r="X330" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y330" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="Y330" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="Z330" t="s" s="2">
-        <v>477</v>
+        <v>506</v>
       </c>
       <c r="AA330" t="s" s="2">
         <v>79</v>
@@ -42591,7 +42627,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="336">
+    <row r="336" hidden="true">
       <c r="A336" t="s" s="2">
         <v>868</v>
       </c>
@@ -42604,13 +42640,13 @@
       </c>
       <c r="E336" s="2"/>
       <c r="F336" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G336" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H336" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I336" t="s" s="2">
         <v>79</v>
@@ -42710,7 +42746,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="337">
+    <row r="337" hidden="true">
       <c r="A337" t="s" s="2">
         <v>870</v>
       </c>
@@ -42723,13 +42759,13 @@
       </c>
       <c r="E337" s="2"/>
       <c r="F337" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G337" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H337" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I337" t="s" s="2">
         <v>79</v>
@@ -42775,11 +42811,13 @@
         <v>79</v>
       </c>
       <c r="X337" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y337" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="Y337" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="Z337" t="s" s="2">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="AA337" t="s" s="2">
         <v>79</v>
@@ -43061,7 +43099,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="340">
+    <row r="340" hidden="true">
       <c r="A340" t="s" s="2">
         <v>874</v>
       </c>
@@ -43074,13 +43112,13 @@
       </c>
       <c r="E340" s="2"/>
       <c r="F340" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G340" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H340" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I340" t="s" s="2">
         <v>79</v>
@@ -43297,7 +43335,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="342">
+    <row r="342" hidden="true">
       <c r="A342" t="s" s="2">
         <v>876</v>
       </c>
@@ -43316,7 +43354,7 @@
         <v>80</v>
       </c>
       <c r="H342" t="s" s="2">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I342" t="s" s="2">
         <v>79</v>
@@ -43479,11 +43517,13 @@
         <v>79</v>
       </c>
       <c r="X343" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y343" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="Y343" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="Z343" t="s" s="2">
-        <v>477</v>
+        <v>506</v>
       </c>
       <c r="AA343" t="s" s="2">
         <v>79</v>

--- a/StructureDefinition-resq-stroke-discharge-composition.xlsx
+++ b/StructureDefinition-resq-stroke-discharge-composition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12876" uniqueCount="879">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12876" uniqueCount="878">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1786,7 +1786,7 @@
     <t>Composition.section:admissionEvaluation.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-diagnosis-condition-profile|http://qualityregistry.org/StructureDefinition/stroke-risk-factor-condition-profile|http://qualityregistry.org/StructureDefinition/functional-score-observation-profile|http://qualityregistry.org/StructureDefinition/vital-sign-observation-profile|http://qualityregistry.org/StructureDefinition/timing-metric-observation-profile|http://qualityregistry.org/StructureDefinition/resq-location-profile|http://qualityregistry.org/StructureDefinition/hospitalized-location-profile)
+    <t xml:space="preserve">Reference(Condition|Observation|Location)
 </t>
   </si>
   <si>
@@ -1847,7 +1847,7 @@
     <t>Composition.section:patientHistory.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/prior-medication-statement-profile|http://qualityregistry.org/StructureDefinition/stroke-risk-factor-condition-profile|http://qualityregistry.org/StructureDefinition/stroke-diagnosis-condition-profile|http://qualityregistry.org/StructureDefinition/post-stroke-complication-condition-profile)
+    <t xml:space="preserve">Reference(Condition|MedicationStatement)
 </t>
   </si>
   <si>
@@ -2040,7 +2040,7 @@
     <t>Composition.section:hospitalCourse.section:diagnosticSummary.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-diagnosis-condition-profile|http://qualityregistry.org/StructureDefinition/stroke-risk-factor-condition-profile|http://qualityregistry.org/StructureDefinition/post-stroke-complication-condition-profile|http://qualityregistry.org/StructureDefinition/specific-finding-observation-profile|http://qualityregistry.org/StructureDefinition/stroke-imaging-diagnostic-report-profile|http://qualityregistry.org/StructureDefinition/mechanical-thrombectomy-diagnostic-report-profile)
+    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
 </t>
   </si>
   <si>
@@ -2101,7 +2101,7 @@
     <t>Composition.section:hospitalCourse.section:significantProcedures.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-imaging-procedure-profile|http://qualityregistry.org/StructureDefinition/stroke-carotid-imaging-procedure-profile|http://qualityregistry.org/StructureDefinition/stroke-carotid-endarterectomy-procedure-profile|http://qualityregistry.org/StructureDefinition/stroke-mechanical-procedure-profile|http://qualityregistry.org/StructureDefinition/stroke-swallow-procedure-profile|http://qualityregistry.org/StructureDefinition/stroke-vte-procedure-profile|http://qualityregistry.org/StructureDefinition/stroke-treatment-procedure-profile)
+    <t xml:space="preserve">Reference(Procedure)
 </t>
   </si>
   <si>
@@ -2162,7 +2162,7 @@
     <t>Composition.section:hospitalCourse.section:treatmentTimings.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/timing-metric-observation-profile)
+    <t xml:space="preserve">Reference(Observation)
 </t>
   </si>
   <si>
@@ -2280,7 +2280,7 @@
     <t>Composition.section:hospitalCourse.section:pharmacotherapy.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-medication-administration-profile|http://qualityregistry.org/StructureDefinition/paracetamol-on-fever-medication-administration-profile|http://qualityregistry.org/StructureDefinition/insulin-on-hyperglycemia-medication-administration-profile|http://qualityregistry.org/StructureDefinition/nimodipine-medication-administration-profile|http://qualityregistry.org/StructureDefinition/anticoagulant-reversal-medication-administration-profile)
+    <t xml:space="preserve">Reference(MedicationAdministration)
 </t>
   </si>
   <si>
@@ -2341,7 +2341,7 @@
     <t>Composition.section:hospitalCourse.section:significantResults.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/specific-finding-observation-profile|http://qualityregistry.org/StructureDefinition/analytics-observation-profile|http://qualityregistry.org/StructureDefinition/fever-observation-profile|http://qualityregistry.org/StructureDefinition/hyperglycemia-observation-profile|http://qualityregistry.org/StructureDefinition/glucose-ge10-observation-profile|http://qualityregistry.org/StructureDefinition/highest-hyperglycemia-value-observation-profile|http://qualityregistry.org/StructureDefinition/highest-systolic-blood-pressure-value-observation-profile|http://qualityregistry.org/StructureDefinition/stroke-imaging-diagnostic-report-profile|http://qualityregistry.org/StructureDefinition/mechanical-thrombectomy-diagnostic-report-profile)
+    <t xml:space="preserve">Reference(Observation|DiagnosticReport)
 </t>
   </si>
   <si>
@@ -2495,10 +2495,6 @@
     <t>Composition.section:dischargeDetails.section:vitalSigns.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/vital-sign-observation-profile|http://qualityregistry.org/StructureDefinition/highest-systolic-blood-pressure-value-observation-profile)
-</t>
-  </si>
-  <si>
     <t>Composition.section:dischargeDetails.section:vitalSigns.emptyReason</t>
   </si>
   <si>
@@ -2670,7 +2666,7 @@
     <t>Composition.section:dischargeDetails.section:functionalStatus.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/functional-score-observation-profile|http://qualityregistry.org/StructureDefinition/glasgow-coma-score-observation-profile|http://qualityregistry.org/StructureDefinition/glasgow-coma-scale-observation-profile|http://qualityregistry.org/StructureDefinition/patient-ventilated-observation-profile|QuestionnaireResponse)
+    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse)
 </t>
   </si>
   <si>
@@ -2731,7 +2727,7 @@
     <t>Composition.section:medicationSummary.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/discharge-medication-request-profile|http://qualityregistry.org/StructureDefinition/no-anticoagulant-discharge-reason-observation-profile)
+    <t xml:space="preserve">Reference(MedicationRequest|Observation)
 </t>
   </si>
   <si>
@@ -2792,7 +2788,7 @@
     <t>Composition.section:planOfCare.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/follow-up-appointment-profile|http://qualityregistry.org/StructureDefinition/three-month-communication-profile|http://qualityregistry.org/StructureDefinition/appointment-management-observation-profile|http://qualityregistry.org/StructureDefinition/three-month-contact-mode-observation-profile|http://qualityregistry.org/StructureDefinition/stroke-treatment-procedure-profile|CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(Appointment|Communication|Observation|Procedure|CarePlan|ServiceRequest)
 </t>
   </si>
   <si>
@@ -3190,7 +3186,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="146.71875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -34183,7 +34179,7 @@
         <v>79</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>771</v>
+        <v>671</v>
       </c>
       <c r="L264" t="s" s="2">
         <v>466</v>
@@ -34274,7 +34270,7 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>617</v>
@@ -34393,7 +34389,7 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>619</v>
@@ -34510,13 +34506,13 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>480</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D267" t="s" s="2">
         <v>79</v>
@@ -34541,7 +34537,7 @@
         <v>337</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="M267" t="s" s="2">
         <v>482</v>
@@ -34629,7 +34625,7 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>597</v>
@@ -34744,7 +34740,7 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>599</v>
@@ -34861,7 +34857,7 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>601</v>
@@ -34980,7 +34976,7 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>603</v>
@@ -35028,7 +35024,7 @@
         <v>79</v>
       </c>
       <c r="S271" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="T271" t="s" s="2">
         <v>79</v>
@@ -35099,7 +35095,7 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>605</v>
@@ -35147,7 +35143,7 @@
         <v>79</v>
       </c>
       <c r="S272" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="T272" t="s" s="2">
         <v>79</v>
@@ -35218,7 +35214,7 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>607</v>
@@ -35335,7 +35331,7 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>609</v>
@@ -35452,7 +35448,7 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>611</v>
@@ -35569,7 +35565,7 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>613</v>
@@ -35688,7 +35684,7 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>615</v>
@@ -35805,7 +35801,7 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>617</v>
@@ -35924,7 +35920,7 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>619</v>
@@ -36041,13 +36037,13 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>480</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D280" t="s" s="2">
         <v>79</v>
@@ -36072,7 +36068,7 @@
         <v>337</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="M280" t="s" s="2">
         <v>482</v>
@@ -36160,7 +36156,7 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>597</v>
@@ -36275,7 +36271,7 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>599</v>
@@ -36392,7 +36388,7 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>601</v>
@@ -36511,7 +36507,7 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>603</v>
@@ -36559,7 +36555,7 @@
         <v>79</v>
       </c>
       <c r="S284" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="T284" t="s" s="2">
         <v>79</v>
@@ -36630,7 +36626,7 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>605</v>
@@ -36678,7 +36674,7 @@
         <v>79</v>
       </c>
       <c r="S285" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="T285" t="s" s="2">
         <v>79</v>
@@ -36749,7 +36745,7 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>607</v>
@@ -36866,7 +36862,7 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>609</v>
@@ -36983,7 +36979,7 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>611</v>
@@ -37100,7 +37096,7 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>613</v>
@@ -37219,7 +37215,7 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>615</v>
@@ -37336,7 +37332,7 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>617</v>
@@ -37455,7 +37451,7 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>619</v>
@@ -37572,13 +37568,13 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>480</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D293" t="s" s="2">
         <v>79</v>
@@ -37603,7 +37599,7 @@
         <v>337</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="M293" t="s" s="2">
         <v>482</v>
@@ -37691,7 +37687,7 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>597</v>
@@ -37806,7 +37802,7 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>599</v>
@@ -37923,7 +37919,7 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>601</v>
@@ -38042,7 +38038,7 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>603</v>
@@ -38090,7 +38086,7 @@
         <v>79</v>
       </c>
       <c r="S297" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="T297" t="s" s="2">
         <v>79</v>
@@ -38161,7 +38157,7 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>605</v>
@@ -38209,7 +38205,7 @@
         <v>79</v>
       </c>
       <c r="S298" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="T298" t="s" s="2">
         <v>79</v>
@@ -38280,7 +38276,7 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>607</v>
@@ -38397,7 +38393,7 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>609</v>
@@ -38514,7 +38510,7 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>611</v>
@@ -38631,7 +38627,7 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>613</v>
@@ -38750,7 +38746,7 @@
     </row>
     <row r="303" hidden="true">
       <c r="A303" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>615</v>
@@ -38776,7 +38772,7 @@
         <v>79</v>
       </c>
       <c r="K303" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="L303" t="s" s="2">
         <v>466</v>
@@ -38867,7 +38863,7 @@
     </row>
     <row r="304" hidden="true">
       <c r="A304" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>617</v>
@@ -38986,7 +38982,7 @@
     </row>
     <row r="305" hidden="true">
       <c r="A305" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>619</v>
@@ -39103,13 +39099,13 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>418</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D306" t="s" s="2">
         <v>79</v>
@@ -39134,7 +39130,7 @@
         <v>337</v>
       </c>
       <c r="L306" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="M306" t="s" s="2">
         <v>488</v>
@@ -39220,7 +39216,7 @@
     </row>
     <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>426</v>
@@ -39335,7 +39331,7 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>427</v>
@@ -39452,7 +39448,7 @@
     </row>
     <row r="309" hidden="true">
       <c r="A309" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>428</v>
@@ -39571,7 +39567,7 @@
     </row>
     <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>429</v>
@@ -39619,7 +39615,7 @@
         <v>79</v>
       </c>
       <c r="S310" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="T310" t="s" s="2">
         <v>79</v>
@@ -39690,7 +39686,7 @@
     </row>
     <row r="311" hidden="true">
       <c r="A311" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>435</v>
@@ -39738,7 +39734,7 @@
         <v>79</v>
       </c>
       <c r="S311" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="T311" t="s" s="2">
         <v>79</v>
@@ -39809,7 +39805,7 @@
     </row>
     <row r="312" hidden="true">
       <c r="A312" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>441</v>
@@ -39926,7 +39922,7 @@
     </row>
     <row r="313" hidden="true">
       <c r="A313" t="s" s="2">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>445</v>
@@ -40043,7 +40039,7 @@
     </row>
     <row r="314" hidden="true">
       <c r="A314" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>451</v>
@@ -40160,7 +40156,7 @@
     </row>
     <row r="315" hidden="true">
       <c r="A315" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>457</v>
@@ -40279,7 +40275,7 @@
     </row>
     <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>465</v>
@@ -40305,7 +40301,7 @@
         <v>79</v>
       </c>
       <c r="K316" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="L316" t="s" s="2">
         <v>466</v>
@@ -40396,7 +40392,7 @@
     </row>
     <row r="317" hidden="true">
       <c r="A317" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>472</v>
@@ -40515,7 +40511,7 @@
     </row>
     <row r="318" hidden="true">
       <c r="A318" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>480</v>
@@ -40632,13 +40628,13 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B319" t="s" s="2">
         <v>418</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D319" t="s" s="2">
         <v>79</v>
@@ -40663,7 +40659,7 @@
         <v>337</v>
       </c>
       <c r="L319" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="M319" t="s" s="2">
         <v>488</v>
@@ -40749,7 +40745,7 @@
     </row>
     <row r="320" hidden="true">
       <c r="A320" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B320" t="s" s="2">
         <v>426</v>
@@ -40864,7 +40860,7 @@
     </row>
     <row r="321" hidden="true">
       <c r="A321" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B321" t="s" s="2">
         <v>427</v>
@@ -40981,7 +40977,7 @@
     </row>
     <row r="322" hidden="true">
       <c r="A322" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B322" t="s" s="2">
         <v>428</v>
@@ -41100,7 +41096,7 @@
     </row>
     <row r="323" hidden="true">
       <c r="A323" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>429</v>
@@ -41148,7 +41144,7 @@
         <v>79</v>
       </c>
       <c r="S323" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="T323" t="s" s="2">
         <v>79</v>
@@ -41219,7 +41215,7 @@
     </row>
     <row r="324" hidden="true">
       <c r="A324" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B324" t="s" s="2">
         <v>435</v>
@@ -41267,7 +41263,7 @@
         <v>79</v>
       </c>
       <c r="S324" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="T324" t="s" s="2">
         <v>79</v>
@@ -41338,7 +41334,7 @@
     </row>
     <row r="325" hidden="true">
       <c r="A325" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B325" t="s" s="2">
         <v>441</v>
@@ -41455,7 +41451,7 @@
     </row>
     <row r="326" hidden="true">
       <c r="A326" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B326" t="s" s="2">
         <v>445</v>
@@ -41572,7 +41568,7 @@
     </row>
     <row r="327" hidden="true">
       <c r="A327" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B327" t="s" s="2">
         <v>451</v>
@@ -41689,7 +41685,7 @@
     </row>
     <row r="328" hidden="true">
       <c r="A328" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B328" t="s" s="2">
         <v>457</v>
@@ -41808,7 +41804,7 @@
     </row>
     <row r="329" hidden="true">
       <c r="A329" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B329" t="s" s="2">
         <v>465</v>
@@ -41834,7 +41830,7 @@
         <v>79</v>
       </c>
       <c r="K329" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="L329" t="s" s="2">
         <v>466</v>
@@ -41925,7 +41921,7 @@
     </row>
     <row r="330" hidden="true">
       <c r="A330" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B330" t="s" s="2">
         <v>472</v>
@@ -42044,7 +42040,7 @@
     </row>
     <row r="331" hidden="true">
       <c r="A331" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B331" t="s" s="2">
         <v>480</v>
@@ -42161,13 +42157,13 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B332" t="s" s="2">
         <v>418</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D332" t="s" s="2">
         <v>79</v>
@@ -42192,7 +42188,7 @@
         <v>337</v>
       </c>
       <c r="L332" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="M332" t="s" s="2">
         <v>488</v>
@@ -42278,7 +42274,7 @@
     </row>
     <row r="333" hidden="true">
       <c r="A333" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B333" t="s" s="2">
         <v>426</v>
@@ -42393,7 +42389,7 @@
     </row>
     <row r="334" hidden="true">
       <c r="A334" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B334" t="s" s="2">
         <v>427</v>
@@ -42510,7 +42506,7 @@
     </row>
     <row r="335" hidden="true">
       <c r="A335" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B335" t="s" s="2">
         <v>428</v>
@@ -42629,7 +42625,7 @@
     </row>
     <row r="336" hidden="true">
       <c r="A336" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B336" t="s" s="2">
         <v>429</v>
@@ -42677,7 +42673,7 @@
         <v>79</v>
       </c>
       <c r="S336" t="s" s="2">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="T336" t="s" s="2">
         <v>79</v>
@@ -42748,7 +42744,7 @@
     </row>
     <row r="337" hidden="true">
       <c r="A337" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B337" t="s" s="2">
         <v>435</v>
@@ -42796,7 +42792,7 @@
         <v>79</v>
       </c>
       <c r="S337" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="T337" t="s" s="2">
         <v>79</v>
@@ -42867,7 +42863,7 @@
     </row>
     <row r="338" hidden="true">
       <c r="A338" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B338" t="s" s="2">
         <v>441</v>
@@ -42984,7 +42980,7 @@
     </row>
     <row r="339" hidden="true">
       <c r="A339" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B339" t="s" s="2">
         <v>445</v>
@@ -43101,7 +43097,7 @@
     </row>
     <row r="340" hidden="true">
       <c r="A340" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B340" t="s" s="2">
         <v>451</v>
@@ -43218,7 +43214,7 @@
     </row>
     <row r="341" hidden="true">
       <c r="A341" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B341" t="s" s="2">
         <v>457</v>
@@ -43337,7 +43333,7 @@
     </row>
     <row r="342" hidden="true">
       <c r="A342" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>465</v>
@@ -43454,7 +43450,7 @@
     </row>
     <row r="343" hidden="true">
       <c r="A343" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B343" t="s" s="2">
         <v>472</v>
@@ -43573,7 +43569,7 @@
     </row>
     <row r="344" hidden="true">
       <c r="A344" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B344" t="s" s="2">
         <v>480</v>

--- a/StructureDefinition-resq-stroke-discharge-composition.xlsx
+++ b/StructureDefinition-resq-stroke-discharge-composition.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-resq-stroke-discharge-composition.xlsx
+++ b/StructureDefinition-resq-stroke-discharge-composition.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
